--- a/data/green_threads_visualization.xlsx
+++ b/data/green_threads_visualization.xlsx
@@ -680,12 +680,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>22.04.2025</t>
+          <t>22/4/2025</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Bundle Pack</t>
+          <t xml:space="preserve">Bundle Pack </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>20.05.2025</t>
+          <t>May 20, 2025</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t xml:space="preserve">Terracotta </t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>24-Feb-2025</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>01-12-2025</t>
+          <t>Jan 12, 2025</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>05-13-2025</t>
+          <t>13/5/2025</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t xml:space="preserve">Shopify </t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>05-21-2025</t>
+          <t>May 21, 2025</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>19.01.2025</t>
+          <t>19-Jan-2025</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>15.01.2025</t>
+          <t>Jan 15, 2025</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>11.02.2025</t>
+          <t>11/2/2025</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>13.06.2025</t>
+          <t>June 13, 2025</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>22.03.2025</t>
+          <t>22-Mar-2025</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>Mar 9, 2025</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>22/5/2025</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>June 5, 2025</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>02-09-2025</t>
+          <t>9-Feb-2025</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>20.05.2025</t>
+          <t>May 20, 2025</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>24/6/2025</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>11.06.2025</t>
+          <t>June 11, 2025</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>21-Mar-2025</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>14.05.2025</t>
+          <t>May 14, 2025</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>23/4/2025</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>April 23, 2025</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>9-Apr-2025</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>28.04.2025</t>
+          <t>Apr 28, 2025</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>14/2/2025</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>02-19-2025</t>
+          <t>February 19, 2025</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>04.05.2025</t>
+          <t>4-May-2025</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>2025-03-09</t>
+          <t>Mar 9, 2025</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>21/6/2025</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>04-11-2025</t>
+          <t>April 11, 2025</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>1-Jun-2025</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>Feb 28, 2025</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>22.03.2025</t>
+          <t>22/3/2025</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>March 28, 2025</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>03-14-2025</t>
+          <t>14-Mar-2025</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>03-14-2025</t>
+          <t>Mar 14, 2025</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>07.05.2025</t>
+          <t>7/5/2025</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>April 24, 2025</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>01-19-2025</t>
+          <t>19-Jan-2025</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>2025-01-27</t>
+          <t>Jan 27, 2025</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>12/3/2025</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>15.04.2025</t>
+          <t>April 15, 2025</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">

--- a/data/green_threads_visualization.xlsx
+++ b/data/green_threads_visualization.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>April 26, 2025</t>
+          <t>26/4/2025</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>May 26, 2025</t>
+          <t>26-May-2025</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>22/4/2025</t>
+          <t>22 Apr 2025</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -732,7 +732,7 @@
       <c r="A6" s="4" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>May 20, 2025</t>
+          <t>20.5.2025</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>17/06/2025</t>
+          <t>17-6-2025</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>June 5, 2025</t>
+          <t>5 Jun, 2025</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>24-Feb-2025</t>
+          <t>24/2/2025</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>13 Apr 2025</t>
+          <t>13-Apr-2025</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Jan 12, 2025</t>
+          <t>12 Jan 2025</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>13/5/2025</t>
+          <t>13.5.2025</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>May 21, 2025</t>
+          <t>21-5-2025</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>19-Jan-2025</t>
+          <t>19 Jan, 2025</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Jan 15, 2025</t>
+          <t>15/1/2025</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>11/2/2025</t>
+          <t>11-Feb-2025</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>June 13, 2025</t>
+          <t>13 Jun 2025</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>3 Jun 2025</t>
+          <t>3.6.2025</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>22-Mar-2025</t>
+          <t>22-3-2025</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Mar 9, 2025</t>
+          <t>9 Mar, 2025</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>June 5, 2025</t>
+          <t>5-Jun-2025</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>10 Apr 2025</t>
+          <t>10.4.2025</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>22 May 2025</t>
+          <t>22-5-2025</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>9-Feb-2025</t>
+          <t>9 Feb, 2025</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>May 20, 2025</t>
+          <t>20/5/2025</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>25/01/2025</t>
+          <t>25-Jan-2025</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>24/6/2025</t>
+          <t>24 Jun 2025</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>June 11, 2025</t>
+          <t>11.6.2025</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>15-5-2025</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>21-Mar-2025</t>
+          <t>21 Mar, 2025</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>May 14, 2025</t>
+          <t>14/5/2025</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>23/4/2025</t>
+          <t>23-Apr-2025</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>April 23, 2025</t>
+          <t>23 Apr 2025</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>9-Apr-2025</t>
+          <t>9.4.2025</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Apr 28, 2025</t>
+          <t>28-4-2025</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>January 1, 2025</t>
+          <t>1 Jan, 2025</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>13/01/2025</t>
+          <t>13/1/2025</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>13/01/2025</t>
+          <t>13-Jan-2025</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>14/2/2025</t>
+          <t>14 Feb 2025</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>May 8, 2025</t>
+          <t>8.5.2025</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>February 19, 2025</t>
+          <t>19-2-2025</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -2992,7 +2992,7 @@
       <c r="A44" s="4" t="inlineStr"/>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>16 Feb 2025</t>
+          <t>16 Feb, 2025</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>25 Feb 2025</t>
+          <t>25/2/2025</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>26 May 2025</t>
+          <t>26-May-2025</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>4-May-2025</t>
+          <t>4 May 2025</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>24/01/2025</t>
+          <t>24.1.2025</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Mar 9, 2025</t>
+          <t>9-3-2025</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -3340,7 +3340,7 @@
       <c r="A50" s="4" t="inlineStr"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>7 Mar, 2025</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>13 May 2025</t>
+          <t>13-May-2025</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>20/06/2025</t>
+          <t>20.6.2025</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>13/05/2025</t>
+          <t>13-5-2025</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>May 25, 2025</t>
+          <t>25 May, 2025</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>April 11, 2025</t>
+          <t>11/4/2025</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>March 9, 2025</t>
+          <t>9-Mar-2025</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>February 25, 2025</t>
+          <t>25 Feb 2025</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>1-Jun-2025</t>
+          <t>1.6.2025</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Feb 28, 2025</t>
+          <t>28-2-2025</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>23 Mar 2025</t>
+          <t>23 Mar, 2025</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>June 1, 2025</t>
+          <t>1-Jun-2025</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>March 28, 2025</t>
+          <t>28 Mar 2025</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>14-Mar-2025</t>
+          <t>14.3.2025</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Mar 14, 2025</t>
+          <t>14-3-2025</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>02/04/2025</t>
+          <t>2 Apr, 2025</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>7/3/2025</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>7/5/2025</t>
+          <t>7-May-2025</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>April 24, 2025</t>
+          <t>24 Apr 2025</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>19-Jan-2025</t>
+          <t>19.1.2025</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>16/03/2025</t>
+          <t>16-3-2025</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -4752,7 +4752,7 @@
       <c r="A74" s="4" t="inlineStr"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>April 7, 2025</t>
+          <t>7 Apr, 2025</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Jan 27, 2025</t>
+          <t>27/1/2025</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>12/3/2025</t>
+          <t>12-Mar-2025</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>April 15, 2025</t>
+          <t>15 Apr 2025</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
